--- a/data/trans_dic/P35-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P35-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que su médico le ha aconsejado hacer algún tipo de ejercicio físico</t>
+          <t>Población a la que su médico le ha aconsejado hacer algún tipo de ejercicio físico (tasa de respuesta: 97,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>27,47; 33,63</t>
+          <t>27,97; 33,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>35,78; 42,66</t>
+          <t>35,86; 42,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>38,63; 45,72</t>
+          <t>38,28; 45,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>38,95; 46,66</t>
+          <t>38,73; 46,48</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>30,2; 35,42</t>
+          <t>30,42; 36,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,2; 48,11</t>
+          <t>42,33; 48,25</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,21; 52,66</t>
+          <t>46,22; 52,84</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>46,07; 51,84</t>
+          <t>46,31; 51,76</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>30,04; 33,83</t>
+          <t>29,99; 33,95</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>40,34; 44,7</t>
+          <t>40,4; 44,54</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>43,92; 48,77</t>
+          <t>43,9; 48,93</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>44,02; 48,59</t>
+          <t>44,06; 48,67</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,65; 12,74</t>
+          <t>9,45; 12,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19,44; 23,29</t>
+          <t>19,35; 23,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22,25; 25,88</t>
+          <t>22,05; 25,96</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20,46; 33,35</t>
+          <t>19,96; 33,24</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,97; 16,73</t>
+          <t>12,89; 16,6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,72; 30,3</t>
+          <t>25,81; 30,19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,46; 31,5</t>
+          <t>27,46; 31,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>21,96; 36,44</t>
+          <t>23,26; 36,19</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11,56; 13,95</t>
+          <t>11,72; 14,09</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22,85; 25,89</t>
+          <t>23,02; 25,91</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25,35; 28,24</t>
+          <t>25,26; 28,14</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>24,01; 33,92</t>
+          <t>24,21; 33,85</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,1; 16,42</t>
+          <t>10,0; 16,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15,06; 23,05</t>
+          <t>15,25; 23,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>20,08; 27,77</t>
+          <t>20,12; 27,58</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>28,1; 35,7</t>
+          <t>28,34; 36,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,87; 16,25</t>
+          <t>9,66; 15,98</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,36; 32,36</t>
+          <t>23,22; 32,85</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23,91; 31,74</t>
+          <t>23,95; 32,03</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>24,64; 30,79</t>
+          <t>24,84; 30,84</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10,74; 15,23</t>
+          <t>10,83; 15,13</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>20,39; 26,06</t>
+          <t>20,39; 26,29</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>23,14; 28,71</t>
+          <t>23,07; 28,69</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>27,3; 32,18</t>
+          <t>27,29; 32,22</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,12; 18,85</t>
+          <t>16,32; 18,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>24,39; 27,59</t>
+          <t>24,32; 27,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26,28; 29,64</t>
+          <t>26,61; 29,54</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25,2; 34,77</t>
+          <t>23,39; 34,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>20,04; 22,99</t>
+          <t>20,12; 22,89</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,65; 35,93</t>
+          <t>32,75; 36,14</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,28; 36,67</t>
+          <t>33,15; 36,49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>27,66; 37,43</t>
+          <t>28,15; 37,41</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>18,67; 20,59</t>
+          <t>18,61; 20,49</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>29,12; 31,51</t>
+          <t>29,15; 31,51</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30,18; 32,67</t>
+          <t>30,43; 32,66</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>28,67; 35,68</t>
+          <t>27,97; 35,31</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que su médico le ha aconsejado hacer algún tipo de ejercicio físico</t>
+          <t>Población a la que su médico le ha aconsejado hacer algún tipo de ejercicio físico (tasa de respuesta: 97,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>269402; 329809</t>
+          <t>274295; 330431</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>341876; 407563</t>
+          <t>342601; 402540</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>285713; 338147</t>
+          <t>283116; 334799</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>200559; 240256</t>
+          <t>199445; 239365</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>378925; 444381</t>
+          <t>381689; 451611</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>548929; 625838</t>
+          <t>550612; 627715</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>454240; 517647</t>
+          <t>454356; 519396</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>346516; 389960</t>
+          <t>348348; 389356</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>671439; 756145</t>
+          <t>670305; 758827</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>910242; 1008478</t>
+          <t>911583; 1005000</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>756519; 840041</t>
+          <t>756232; 842833</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>557773; 615692</t>
+          <t>558262; 616681</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>155739; 205725</t>
+          <t>152594; 203328</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>368569; 441516</t>
+          <t>366811; 444109</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>455530; 529857</t>
+          <t>451587; 531541</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>468696; 763917</t>
+          <t>457230; 761268</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>194773; 251222</t>
+          <t>193512; 249139</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>437857; 515985</t>
+          <t>439464; 514074</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>539916; 619459</t>
+          <t>540046; 620586</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>491046; 814688</t>
+          <t>520033; 809253</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>360054; 434596</t>
+          <t>365138; 439053</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>822148; 931649</t>
+          <t>828487; 932244</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1017530; 1133702</t>
+          <t>1014070; 1129644</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1086852; 1535456</t>
+          <t>1095693; 1531956</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>53715; 87369</t>
+          <t>53202; 85294</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>70683; 108143</t>
+          <t>71558; 108611</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>107539; 148681</t>
+          <t>107718; 147704</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>181704; 230851</t>
+          <t>183224; 233307</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>44633; 73486</t>
+          <t>43680; 72282</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>103830; 143809</t>
+          <t>103194; 146021</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>128206; 170157</t>
+          <t>128400; 171727</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>162653; 203244</t>
+          <t>163961; 203549</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>105724; 149935</t>
+          <t>106642; 148899</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>186268; 238142</t>
+          <t>186293; 240238</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>248017; 307651</t>
+          <t>247267; 307420</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>356717; 420449</t>
+          <t>356537; 421003</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>504055; 589433</t>
+          <t>510422; 590682</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>809778; 915975</t>
+          <t>807657; 916579</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>873269; 985004</t>
+          <t>884028; 981573</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>869759; 1200154</t>
+          <t>807426; 1187733</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>643049; 737446</t>
+          <t>645355; 734471</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1125842; 1238727</t>
+          <t>1129221; 1246086</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1160099; 1278195</t>
+          <t>1155594; 1271794</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1009101; 1365611</t>
+          <t>1026819; 1364688</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1182969; 1304283</t>
+          <t>1178787; 1297968</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1971237; 2132952</t>
+          <t>1973336; 2132675</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2054854; 2224443</t>
+          <t>2071841; 2223407</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2035421; 2533292</t>
+          <t>1985986; 2507032</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P35-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P35-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>41,11%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>48,64%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>45,53%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>27,97; 33,69</t>
+          <t>27,81; 33,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>35,86; 42,13</t>
+          <t>35,79; 42,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>38,28; 45,27</t>
+          <t>38,47; 45,76</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>38,73; 46,48</t>
+          <t>37,08; 45,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>30,42; 36,0</t>
+          <t>30,41; 35,48</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,33; 48,25</t>
+          <t>41,88; 47,74</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,22; 52,84</t>
+          <t>46,1; 52,98</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>46,31; 51,76</t>
+          <t>46,01; 51,35</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>29,99; 33,95</t>
+          <t>29,96; 33,96</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>40,4; 44,54</t>
+          <t>40,29; 44,63</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>43,9; 48,93</t>
+          <t>43,82; 48,74</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>44,06; 48,67</t>
+          <t>43,13; 47,72</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>35,16%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,45; 12,59</t>
+          <t>9,57; 12,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19,35; 23,42</t>
+          <t>19,39; 23,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22,05; 25,96</t>
+          <t>22,19; 26,07</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19,96; 33,24</t>
+          <t>31,22; 35,53</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,89; 16,6</t>
+          <t>12,97; 16,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,81; 30,19</t>
+          <t>25,94; 30,24</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,46; 31,56</t>
+          <t>27,53; 31,68</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>23,26; 36,19</t>
+          <t>35,05; 38,98</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11,72; 14,09</t>
+          <t>11,61; 14,11</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23,02; 25,91</t>
+          <t>23,03; 25,92</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25,26; 28,14</t>
+          <t>25,27; 28,04</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>24,21; 33,85</t>
+          <t>33,52; 36,57</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>30,32%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,0; 16,03</t>
+          <t>10,3; 16,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15,25; 23,15</t>
+          <t>15,05; 23,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>20,12; 27,58</t>
+          <t>20,01; 27,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>28,34; 36,08</t>
+          <t>29,12; 36,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,66; 15,98</t>
+          <t>9,91; 15,98</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,22; 32,85</t>
+          <t>23,87; 32,56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23,95; 32,03</t>
+          <t>24,21; 32,1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>24,84; 30,84</t>
+          <t>25,27; 31,3</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10,83; 15,13</t>
+          <t>10,79; 15,34</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>20,39; 26,29</t>
+          <t>20,23; 26,12</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>23,07; 28,69</t>
+          <t>23,16; 28,57</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>27,29; 32,22</t>
+          <t>28,15; 32,9</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>36,2%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,32; 18,89</t>
+          <t>16,28; 18,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>24,32; 27,6</t>
+          <t>24,31; 27,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26,61; 29,54</t>
+          <t>26,4; 29,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23,39; 34,41</t>
+          <t>32,7; 36,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>20,12; 22,89</t>
+          <t>20,18; 23,21</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,75; 36,14</t>
+          <t>32,8; 36,03</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,15; 36,49</t>
+          <t>33,35; 36,65</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>28,15; 37,41</t>
+          <t>36,53; 39,27</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>18,61; 20,49</t>
+          <t>18,61; 20,5</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>29,15; 31,51</t>
+          <t>29,09; 31,47</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30,43; 32,66</t>
+          <t>30,31; 32,66</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>27,97; 35,31</t>
+          <t>35,11; 37,26</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>218432</t>
+          <t>237854</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>368488</t>
+          <t>399021</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>586920</t>
+          <t>636876</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>274295; 330431</t>
+          <t>272725; 327560</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>342601; 402540</t>
+          <t>341895; 403234</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>283116; 334799</t>
+          <t>284508; 338424</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>199445; 239365</t>
+          <t>214507; 261348</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>381689; 451611</t>
+          <t>381519; 445083</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>550612; 627715</t>
+          <t>544749; 621047</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>454356; 519396</t>
+          <t>453139; 520816</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>348348; 389356</t>
+          <t>377450; 421224</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>670305; 758827</t>
+          <t>669684; 759069</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>911583; 1005000</t>
+          <t>908989; 1006934</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>756232; 842833</t>
+          <t>754845; 839533</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>558262; 616681</t>
+          <t>603328; 667569</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>665122</t>
+          <t>743060</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>709944</t>
+          <t>804108</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1375066</t>
+          <t>1547168</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>152594; 203328</t>
+          <t>154453; 205775</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>366811; 444109</t>
+          <t>367580; 440514</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>451587; 531541</t>
+          <t>454338; 533849</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>457230; 761268</t>
+          <t>696483; 792526</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>193512; 249139</t>
+          <t>194711; 248863</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>439464; 514074</t>
+          <t>441627; 514963</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>540046; 620586</t>
+          <t>541317; 622923</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>520033; 809253</t>
+          <t>760373; 845579</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>365138; 439053</t>
+          <t>361878; 439564</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>828487; 932244</t>
+          <t>828601; 932761</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1014070; 1129644</t>
+          <t>1014420; 1125703</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1095693; 1531956</t>
+          <t>1474968; 1609196</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>206304</t>
+          <t>231695</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>182087</t>
+          <t>206738</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>388392</t>
+          <t>438433</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>53202; 85294</t>
+          <t>54776; 85125</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>71558; 108611</t>
+          <t>70644; 108168</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>107718; 147704</t>
+          <t>107175; 148976</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>183224; 233307</t>
+          <t>207192; 259240</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>43680; 72282</t>
+          <t>44827; 72282</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>103194; 146021</t>
+          <t>106098; 144709</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>128400; 171727</t>
+          <t>129772; 172072</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>163961; 203549</t>
+          <t>185576; 229867</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>106642; 148899</t>
+          <t>106229; 151014</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>186293; 240238</t>
+          <t>184855; 238639</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>247267; 307420</t>
+          <t>248233; 306154</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>356537; 421003</t>
+          <t>407055; 475761</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1089858</t>
+          <t>1212610</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1260519</t>
+          <t>1409867</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2350378</t>
+          <t>2622476</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>510422; 590682</t>
+          <t>508961; 587680</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>807657; 916579</t>
+          <t>807358; 915639</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>884028; 981573</t>
+          <t>877168; 985925</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>807426; 1187733</t>
+          <t>1151181; 1277155</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>645355; 734471</t>
+          <t>647402; 744599</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1129221; 1246086</t>
+          <t>1131012; 1242262</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1155594; 1271794</t>
+          <t>1162432; 1277355</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1026819; 1364688</t>
+          <t>1360566; 1462509</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1178787; 1297968</t>
+          <t>1179306; 1298809</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1973336; 2132675</t>
+          <t>1969199; 2130325</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2071841; 2223407</t>
+          <t>2063326; 2223349</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1985986; 2507032</t>
+          <t>2544011; 2699647</t>
         </is>
       </c>
     </row>
